--- a/Build/POS.xlsx
+++ b/Build/POS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\SimpleCodec\Build\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electronica\PicoFX\Build\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{548EBF21-D701-42C3-8D6E-4EE5B4E43C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4E18BF-1962-479D-B56F-382F3E8EF0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="19200" windowHeight="11170" xr2:uid="{2FF5DDB3-5F6F-4B26-A214-40B236386A43}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{2FF5DDB3-5F6F-4B26-A214-40B236386A43}"/>
   </bookViews>
   <sheets>
     <sheet name="POS" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="94">
   <si>
     <t>Designator</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t>U5</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>J2</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9456C5-8C57-459D-A439-BB7A21AA9EC6}">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1186,13 +1192,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>147.80000000000001</v>
+        <v>144.80000000000001</v>
       </c>
       <c r="C2">
-        <v>-59.75</v>
+        <v>-67.599999999999994</v>
       </c>
       <c r="D2">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -1203,13 +1209,13 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>151.65</v>
+        <v>154.80000000000001</v>
       </c>
       <c r="C3">
-        <v>-64.599999999999994</v>
+        <v>-67.599999999999994</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -1220,13 +1226,13 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>152.6</v>
+        <v>147.6</v>
       </c>
       <c r="C4">
         <v>-67.599999999999994</v>
       </c>
       <c r="D4">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -1237,10 +1243,10 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>147.6</v>
+        <v>152.6</v>
       </c>
       <c r="C5">
-        <v>-71.599999999999994</v>
+        <v>-67.599999999999994</v>
       </c>
       <c r="D5">
         <v>90</v>
@@ -1257,10 +1263,10 @@
         <v>147.6</v>
       </c>
       <c r="C6">
-        <v>-75.599999999999994</v>
+        <v>-71.599999999999994</v>
       </c>
       <c r="D6">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -1271,13 +1277,13 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>144.6</v>
+        <v>147.6</v>
       </c>
       <c r="C7">
-        <v>-71.599999999999994</v>
+        <v>-75.599999999999994</v>
       </c>
       <c r="D7">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -1288,13 +1294,13 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>122.8</v>
+        <v>127.2</v>
       </c>
       <c r="C8">
-        <v>-98.4</v>
+        <v>-91.8</v>
       </c>
       <c r="D8">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -1308,10 +1314,10 @@
         <v>144.6</v>
       </c>
       <c r="C9">
-        <v>-75.599999999999994</v>
+        <v>-71.599999999999994</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -1322,10 +1328,10 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>144.6</v>
+        <v>127.2</v>
       </c>
       <c r="C10">
-        <v>-77.8</v>
+        <v>-94.6</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -1339,13 +1345,13 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>122.8</v>
+        <v>144.6</v>
       </c>
       <c r="C11">
-        <v>-102.4</v>
+        <v>-75.599999999999994</v>
       </c>
       <c r="D11">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -1356,10 +1362,10 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>128.19999999999999</v>
+        <v>122.8</v>
       </c>
       <c r="C12">
-        <v>-71.400000000000006</v>
+        <v>-98.4</v>
       </c>
       <c r="D12">
         <v>90</v>
@@ -1373,13 +1379,13 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>135.80000000000001</v>
+        <v>144.6</v>
       </c>
       <c r="C13">
-        <v>-71.400000000000006</v>
+        <v>-77.8</v>
       </c>
       <c r="D13">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -1390,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>125.8</v>
+        <v>148.19999999999999</v>
       </c>
       <c r="C14">
-        <v>-71.400000000000006</v>
+        <v>-80.599999999999994</v>
       </c>
       <c r="D14">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -1407,10 +1413,10 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>138.19999999999999</v>
+        <v>122.8</v>
       </c>
       <c r="C15">
-        <v>-71.400000000000006</v>
+        <v>-102.4</v>
       </c>
       <c r="D15">
         <v>-90</v>
@@ -1424,13 +1430,13 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>127</v>
+        <v>128.19999999999999</v>
       </c>
       <c r="C16">
-        <v>-83.2</v>
+        <v>-71.400000000000006</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -1441,13 +1447,13 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>137</v>
+        <v>135.80000000000001</v>
       </c>
       <c r="C17">
-        <v>-83.2</v>
+        <v>-71.400000000000006</v>
       </c>
       <c r="D17">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -1458,13 +1464,13 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>132</v>
+        <v>125.8</v>
       </c>
       <c r="C18">
-        <v>-83</v>
+        <v>-71.400000000000006</v>
       </c>
       <c r="D18">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
@@ -1475,13 +1481,13 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>167</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="C19">
-        <v>-74.2</v>
+        <v>-71.400000000000006</v>
       </c>
       <c r="D19">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -1492,13 +1498,13 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="C20">
-        <v>-74.2</v>
+        <v>-83.2</v>
       </c>
       <c r="D20">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -1509,13 +1515,13 @@
         <v>25</v>
       </c>
       <c r="B21">
-        <v>162.80000000000001</v>
+        <v>137</v>
       </c>
       <c r="C21">
-        <v>-79.599999999999994</v>
+        <v>-83.2</v>
       </c>
       <c r="D21">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
@@ -1526,13 +1532,13 @@
         <v>26</v>
       </c>
       <c r="B22">
-        <v>173.2</v>
+        <v>132</v>
       </c>
       <c r="C22">
-        <v>-79.599999999999994</v>
+        <v>-83</v>
       </c>
       <c r="D22">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -1543,13 +1549,13 @@
         <v>27</v>
       </c>
       <c r="B23">
-        <v>165.2</v>
+        <v>167</v>
       </c>
       <c r="C23">
-        <v>-69.2</v>
+        <v>-74.2</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -1560,13 +1566,13 @@
         <v>28</v>
       </c>
       <c r="B24">
-        <v>170.8</v>
+        <v>169</v>
       </c>
       <c r="C24">
-        <v>-69.2</v>
+        <v>-74.2</v>
       </c>
       <c r="D24">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -1577,13 +1583,13 @@
         <v>29</v>
       </c>
       <c r="B25">
-        <v>161.6</v>
+        <v>162.80000000000001</v>
       </c>
       <c r="C25">
-        <v>-69.2</v>
+        <v>-79.599999999999994</v>
       </c>
       <c r="D25">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
@@ -1594,13 +1600,13 @@
         <v>30</v>
       </c>
       <c r="B26">
-        <v>174.4</v>
+        <v>173.2</v>
       </c>
       <c r="C26">
-        <v>-69.2</v>
+        <v>-79.599999999999994</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
@@ -1611,13 +1617,13 @@
         <v>31</v>
       </c>
       <c r="B27">
-        <v>168</v>
+        <v>165.2</v>
       </c>
       <c r="C27">
-        <v>-83</v>
+        <v>-69.2</v>
       </c>
       <c r="D27">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E27" t="s">
         <v>6</v>
@@ -1628,10 +1634,10 @@
         <v>32</v>
       </c>
       <c r="B28">
-        <v>151.80000000000001</v>
+        <v>170.8</v>
       </c>
       <c r="C28">
-        <v>-103.4</v>
+        <v>-69.2</v>
       </c>
       <c r="D28">
         <v>180</v>
@@ -1645,13 +1651,13 @@
         <v>33</v>
       </c>
       <c r="B29">
-        <v>148.19999999999999</v>
+        <v>161.6</v>
       </c>
       <c r="C29">
-        <v>-103.4</v>
+        <v>-69.2</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E29" t="s">
         <v>6</v>
@@ -1662,10 +1668,10 @@
         <v>34</v>
       </c>
       <c r="B30">
-        <v>151.6</v>
+        <v>174.4</v>
       </c>
       <c r="C30">
-        <v>-101.4</v>
+        <v>-69.2</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1679,10 +1685,10 @@
         <v>35</v>
       </c>
       <c r="B31">
-        <v>148.4</v>
+        <v>168</v>
       </c>
       <c r="C31">
-        <v>-101.4</v>
+        <v>-83</v>
       </c>
       <c r="D31">
         <v>180</v>
@@ -1696,13 +1702,13 @@
         <v>36</v>
       </c>
       <c r="B32">
-        <v>139</v>
+        <v>151.80000000000001</v>
       </c>
       <c r="C32">
-        <v>-80.400000000000006</v>
+        <v>-103.4</v>
       </c>
       <c r="D32">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
@@ -1713,13 +1719,13 @@
         <v>37</v>
       </c>
       <c r="B33">
-        <v>148.4</v>
+        <v>148.19999999999999</v>
       </c>
       <c r="C33">
-        <v>-85</v>
+        <v>-103.4</v>
       </c>
       <c r="D33">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E33" t="s">
         <v>6</v>
@@ -1730,13 +1736,13 @@
         <v>38</v>
       </c>
       <c r="B34">
-        <v>143.4</v>
+        <v>151.6</v>
       </c>
       <c r="C34">
-        <v>-91.2</v>
+        <v>-101.4</v>
       </c>
       <c r="D34">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
@@ -1747,10 +1753,10 @@
         <v>39</v>
       </c>
       <c r="B35">
-        <v>151.6</v>
+        <v>148.4</v>
       </c>
       <c r="C35">
-        <v>-85</v>
+        <v>-101.4</v>
       </c>
       <c r="D35">
         <v>180</v>
@@ -1764,7 +1770,7 @@
         <v>40</v>
       </c>
       <c r="B36">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="C36">
         <v>-80.400000000000006</v>
@@ -1781,13 +1787,13 @@
         <v>41</v>
       </c>
       <c r="B37">
-        <v>148.19999999999999</v>
+        <v>148.4</v>
       </c>
       <c r="C37">
-        <v>-83</v>
+        <v>-85</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E37" t="s">
         <v>6</v>
@@ -1798,10 +1804,10 @@
         <v>42</v>
       </c>
       <c r="B38">
-        <v>141.4</v>
+        <v>143.4</v>
       </c>
       <c r="C38">
-        <v>-91.025000000000006</v>
+        <v>-91.2</v>
       </c>
       <c r="D38">
         <v>-90</v>
@@ -1815,13 +1821,13 @@
         <v>43</v>
       </c>
       <c r="B39">
-        <v>151.80000000000001</v>
+        <v>151.6</v>
       </c>
       <c r="C39">
-        <v>-83</v>
+        <v>-85</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E39" t="s">
         <v>6</v>
@@ -1832,13 +1838,13 @@
         <v>44</v>
       </c>
       <c r="B40">
-        <v>127.2</v>
+        <v>125</v>
       </c>
       <c r="C40">
-        <v>-91.8</v>
+        <v>-80.400000000000006</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E40" t="s">
         <v>6</v>
@@ -1849,10 +1855,10 @@
         <v>45</v>
       </c>
       <c r="B41">
-        <v>127.2</v>
+        <v>148.19999999999999</v>
       </c>
       <c r="C41">
-        <v>-94.6</v>
+        <v>-83</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1866,13 +1872,13 @@
         <v>46</v>
       </c>
       <c r="B42">
-        <v>154.80000000000001</v>
+        <v>141.4</v>
       </c>
       <c r="C42">
-        <v>-67.599999999999994</v>
+        <v>-91.025000000000006</v>
       </c>
       <c r="D42">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E42" t="s">
         <v>6</v>
@@ -1883,10 +1889,10 @@
         <v>47</v>
       </c>
       <c r="B43">
-        <v>148.19999999999999</v>
+        <v>151.80000000000001</v>
       </c>
       <c r="C43">
-        <v>-80.599999999999994</v>
+        <v>-83</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1900,10 +1906,10 @@
         <v>48</v>
       </c>
       <c r="B44">
-        <v>151.80000000000001</v>
+        <v>150.4</v>
       </c>
       <c r="C44">
-        <v>-58.8</v>
+        <v>-59.2</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1917,10 +1923,10 @@
         <v>49</v>
       </c>
       <c r="B45">
-        <v>151.80000000000001</v>
+        <v>150.4</v>
       </c>
       <c r="C45">
-        <v>-61.6</v>
+        <v>-61.8</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2002,13 +2008,13 @@
         <v>54</v>
       </c>
       <c r="B50">
-        <v>147.80000000000001</v>
+        <v>146.19999999999999</v>
       </c>
       <c r="C50">
-        <v>-63.2</v>
+        <v>-64.8</v>
       </c>
       <c r="D50">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E50" t="s">
         <v>6</v>
@@ -2019,13 +2025,13 @@
         <v>55</v>
       </c>
       <c r="B51">
-        <v>144.6</v>
+        <v>124.4</v>
       </c>
       <c r="C51">
-        <v>-73.599999999999994</v>
+        <v>-93.2</v>
       </c>
       <c r="D51">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="E51" t="s">
         <v>6</v>
@@ -2036,13 +2042,13 @@
         <v>56</v>
       </c>
       <c r="B52">
-        <v>124.4</v>
+        <v>144.6</v>
       </c>
       <c r="C52">
-        <v>-93.2</v>
+        <v>-73.599999999999994</v>
       </c>
       <c r="D52">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="E52" t="s">
         <v>6</v>
@@ -2050,13 +2056,13 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="B53">
-        <v>143.4</v>
+        <v>161.19999999999999</v>
       </c>
       <c r="C53">
-        <v>-95.2</v>
+        <v>-132</v>
       </c>
       <c r="D53">
         <v>90</v>
@@ -2067,16 +2073,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B54">
-        <v>150.6</v>
+        <v>137.19999999999999</v>
       </c>
       <c r="C54">
-        <v>-67.599999999999994</v>
+        <v>-132</v>
       </c>
       <c r="D54">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E54" t="s">
         <v>6</v>
@@ -2084,16 +2090,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B55">
-        <v>128.19999999999999</v>
+        <v>143.4</v>
       </c>
       <c r="C55">
-        <v>-68</v>
+        <v>-95.2</v>
       </c>
       <c r="D55">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E55" t="s">
         <v>6</v>
@@ -2101,13 +2107,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B56">
-        <v>138.19999999999999</v>
+        <v>150.6</v>
       </c>
       <c r="C56">
-        <v>-68</v>
+        <v>-67.599999999999994</v>
       </c>
       <c r="D56">
         <v>-90</v>
@@ -2118,16 +2124,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B57">
-        <v>125.8</v>
+        <v>128.19999999999999</v>
       </c>
       <c r="C57">
         <v>-68</v>
       </c>
       <c r="D57">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E57" t="s">
         <v>6</v>
@@ -2135,16 +2141,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B58">
-        <v>135.80000000000001</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="C58">
         <v>-68</v>
       </c>
       <c r="D58">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="E58" t="s">
         <v>6</v>
@@ -2152,13 +2158,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B59">
-        <v>131</v>
+        <v>125.8</v>
       </c>
       <c r="C59">
-        <v>-74.2</v>
+        <v>-68</v>
       </c>
       <c r="D59">
         <v>90</v>
@@ -2169,13 +2175,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B60">
-        <v>133</v>
+        <v>135.80000000000001</v>
       </c>
       <c r="C60">
-        <v>-74.2</v>
+        <v>-68</v>
       </c>
       <c r="D60">
         <v>90</v>
@@ -2186,16 +2192,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B61">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C61">
-        <v>-80.400000000000006</v>
+        <v>-74.2</v>
       </c>
       <c r="D61">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E61" t="s">
         <v>6</v>
@@ -2203,16 +2209,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B62">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C62">
-        <v>-80.400000000000006</v>
+        <v>-74.2</v>
       </c>
       <c r="D62">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="E62" t="s">
         <v>6</v>
@@ -2220,16 +2226,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B63">
-        <v>157.6</v>
+        <v>127</v>
       </c>
       <c r="C63">
-        <v>-83.8</v>
+        <v>-80.400000000000006</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E63" t="s">
         <v>6</v>
@@ -2237,16 +2243,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B64">
-        <v>157.6</v>
+        <v>137</v>
       </c>
       <c r="C64">
-        <v>-85.4</v>
+        <v>-80.400000000000006</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E64" t="s">
         <v>6</v>
@@ -2254,13 +2260,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B65">
-        <v>168</v>
+        <v>157.6</v>
       </c>
       <c r="C65">
-        <v>-89.6</v>
+        <v>-83.8</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2271,13 +2277,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B66">
-        <v>168</v>
+        <v>157.6</v>
       </c>
       <c r="C66">
-        <v>-88</v>
+        <v>-85.4</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2288,13 +2294,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B67">
-        <v>164.6</v>
+        <v>168</v>
       </c>
       <c r="C67">
-        <v>-73.400000000000006</v>
+        <v>-89.6</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2305,16 +2311,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B68">
-        <v>171.4</v>
+        <v>168</v>
       </c>
       <c r="C68">
-        <v>-73.400000000000006</v>
+        <v>-88</v>
       </c>
       <c r="D68">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E68" t="s">
         <v>6</v>
@@ -2322,16 +2328,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B69">
-        <v>161.19999999999999</v>
+        <v>164.6</v>
       </c>
       <c r="C69">
-        <v>-79.599999999999994</v>
+        <v>-73.400000000000006</v>
       </c>
       <c r="D69">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E69" t="s">
         <v>6</v>
@@ -2339,16 +2345,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B70">
-        <v>164.6</v>
+        <v>171.4</v>
       </c>
       <c r="C70">
-        <v>-75</v>
+        <v>-73.400000000000006</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E70" t="s">
         <v>6</v>
@@ -2356,10 +2362,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B71">
-        <v>174.8</v>
+        <v>161.19999999999999</v>
       </c>
       <c r="C71">
         <v>-79.599999999999994</v>
@@ -2373,16 +2379,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B72">
-        <v>171.4</v>
+        <v>164.6</v>
       </c>
       <c r="C72">
         <v>-75</v>
       </c>
       <c r="D72">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E72" t="s">
         <v>6</v>
@@ -2390,16 +2396,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B73">
-        <v>162</v>
+        <v>174.8</v>
       </c>
       <c r="C73">
-        <v>-82</v>
+        <v>-79.599999999999994</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E73" t="s">
         <v>6</v>
@@ -2407,13 +2413,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B74">
-        <v>174</v>
+        <v>171.4</v>
       </c>
       <c r="C74">
-        <v>-82</v>
+        <v>-75</v>
       </c>
       <c r="D74">
         <v>180</v>
@@ -2424,16 +2430,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B75">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C75">
-        <v>-67.2</v>
+        <v>-82</v>
       </c>
       <c r="D75">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E75" t="s">
         <v>6</v>
@@ -2441,16 +2447,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B76">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C76">
-        <v>-67.2</v>
+        <v>-82</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E76" t="s">
         <v>6</v>
@@ -2458,10 +2464,10 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B77">
-        <v>161.80000000000001</v>
+        <v>165</v>
       </c>
       <c r="C77">
         <v>-67.2</v>
@@ -2475,10 +2481,10 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B78">
-        <v>174.2</v>
+        <v>171</v>
       </c>
       <c r="C78">
         <v>-67.2</v>
@@ -2492,16 +2498,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B79">
-        <v>143.4</v>
+        <v>161.80000000000001</v>
       </c>
       <c r="C79">
-        <v>-101.4</v>
+        <v>-67.2</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E79" t="s">
         <v>6</v>
@@ -2509,13 +2515,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B80">
-        <v>143.4</v>
+        <v>174.2</v>
       </c>
       <c r="C80">
-        <v>-99.4</v>
+        <v>-67.2</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2526,16 +2532,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B81">
-        <v>156.6</v>
+        <v>143.4</v>
       </c>
       <c r="C81">
-        <v>-91.2</v>
+        <v>-101.4</v>
       </c>
       <c r="D81">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="E81" t="s">
         <v>6</v>
@@ -2543,16 +2549,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B82">
-        <v>154.6</v>
+        <v>143.4</v>
       </c>
       <c r="C82">
-        <v>-83</v>
+        <v>-99.4</v>
       </c>
       <c r="D82">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E82" t="s">
         <v>6</v>
@@ -2560,16 +2566,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B83">
-        <v>153.80000000000001</v>
+        <v>156.6</v>
       </c>
       <c r="C83">
-        <v>-73.599999999999994</v>
+        <v>-91.2</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="E83" t="s">
         <v>6</v>
@@ -2577,16 +2583,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B84">
-        <v>129</v>
+        <v>154.6</v>
       </c>
       <c r="C84">
-        <v>-100.4</v>
+        <v>-83</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E84" t="s">
         <v>6</v>
@@ -2594,13 +2600,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B85">
-        <v>132</v>
+        <v>153.80000000000001</v>
       </c>
       <c r="C85">
-        <v>-79</v>
+        <v>-73.599999999999994</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -2611,13 +2617,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B86">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="C86">
-        <v>-79</v>
+        <v>-100.4</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2628,18 +2634,52 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
+        <v>89</v>
+      </c>
+      <c r="B87">
+        <v>132</v>
+      </c>
+      <c r="C87">
+        <v>-79</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>90</v>
+      </c>
+      <c r="B88">
+        <v>168</v>
+      </c>
+      <c r="C88">
+        <v>-79</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>91</v>
       </c>
-      <c r="B87">
+      <c r="B89">
         <v>150</v>
       </c>
-      <c r="C87">
+      <c r="C89">
         <v>-93.2</v>
       </c>
-      <c r="D87">
+      <c r="D89">
         <v>90</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E89" t="s">
         <v>6</v>
       </c>
     </row>
